--- a/output/pdf_financials_xlsx/MCI.xlsx
+++ b/output/pdf_financials_xlsx/MCI.xlsx
@@ -4451,40 +4451,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.092012</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.193017</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.267291</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.500201</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.999687</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.0574</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.713124</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.470002</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.061614</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.739845</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.473091</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.443843</v>
       </c>
     </row>
     <row r="93">
@@ -7234,7 +7234,11 @@
           <t>Share-based payment reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -7970,7 +7974,11 @@
           <t>Share-based payment reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -8796,7 +8804,11 @@
           <t>Share-based payment reserves (Note 15)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -9616,7 +9628,11 @@
           <t>Share-based payment reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -10188,7 +10204,11 @@
           <t>Share-based payment reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>1.092012</v>
       </c>
@@ -10470,7 +10490,11 @@
           <t>Share-based payment reserves (Notes 11 and 13)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -10836,7 +10860,11 @@
           <t>Share-based payment reserves (Notes 12 and 14)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MCI.xlsx
+++ b/output/pdf_financials_xlsx/MCI.xlsx
@@ -915,13 +915,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00666</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.004125</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -930,7 +930,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1620,13 +1620,13 @@
         <v>-0.439248</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.413542</v>
+        <v>-0.420202</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.166992</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.057203</v>
+        <v>-0.061328</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-1.766895</v>
@@ -1635,7 +1635,7 @@
         <v>-0.374981</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.750127</v>
+        <v>-0.750158</v>
       </c>
     </row>
     <row r="28">
@@ -1706,13 +1706,13 @@
         <v>-0.439248</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.413542</v>
+        <v>-0.420202</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.166992</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.057203</v>
+        <v>-0.061328</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-1.766895</v>
@@ -1721,7 +1721,7 @@
         <v>-0.374981</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.750127</v>
+        <v>-0.750158</v>
       </c>
     </row>
     <row r="30">
@@ -1933,22 +1933,22 @@
         <v>0.033973</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.021039</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.13145</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.138038</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.129726</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.001378</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.003556</v>
       </c>
     </row>
     <row r="35">
@@ -2019,22 +2019,22 @@
         <v>0.033973</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.021039</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.13145</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.138038</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.129726</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.001378</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.003556</v>
       </c>
     </row>
     <row r="37">
@@ -2535,22 +2535,22 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.032043</v>
+        <v>0.011004</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.310381</v>
+        <v>0.178931</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.282317</v>
+        <v>0.144279</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.133068</v>
+        <v>0.003342</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.001378</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.003556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">

--- a/output/pdf_financials_xlsx/MCI.xlsx
+++ b/output/pdf_financials_xlsx/MCI.xlsx
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.057511</v>
+        <v>-0.057511</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.025772</v>
+        <v>-0.025772</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -3382,16 +3382,16 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.281799</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.281332</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.362512</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.377011</v>
       </c>
     </row>
     <row r="68">
@@ -5241,7 +5241,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.105</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -6254,7 +6254,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.105</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -6297,7 +6297,7 @@
         <v>-0.342465</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.664708</v>
+        <v>-0.7697079999999999</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.847441</v>
@@ -17406,7 +17406,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -17862,7 +17866,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="n">
         <v>-0.057511</v>
       </c>
@@ -26440,7 +26448,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -27426,7 +27438,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E288" s="5" t="n">
         <v>0.057511</v>
       </c>
